--- a/school_surveys/012_school_partnership_perception_survey--school_surveys.xlsx
+++ b/school_surveys/012_school_partnership_perception_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'highly_satisfied',_'label':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Satisfied', 'label': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'moderately_satisfied',_'label':_'moderately_satisfied'}</t>
+          <t>moderately_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Moderately Satisfied', 'label': 'Moderately Satisfied'}</t>
+          <t>Moderately Satisfied</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_satisfied',_'label':_'not_at_all_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Satisfied', 'label': 'Not at all Satisfied'}</t>
+          <t>Not at all Satisfied</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'highly_involved',_'label':_'highly_involved'}</t>
+          <t>highly_involved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Involved', 'label': 'Highly Involved'}</t>
+          <t>Highly Involved</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'moderately_involved',_'label':_'moderately_involved'}</t>
+          <t>moderately_involved</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Moderately Involved', 'label': 'Moderately Involved'}</t>
+          <t>Moderately Involved</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_involved',_'label':_'not_at_all_involved'}</t>
+          <t>not_at_all_involved</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Involved', 'label': 'Not at all Involved'}</t>
+          <t>Not at all Involved</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'highly_aware',_'label':_'highly_aware'}</t>
+          <t>highly_aware</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Aware', 'label': 'Highly Aware'}</t>
+          <t>Highly Aware</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'moderately_aware',_'label':_'moderately_aware'}</t>
+          <t>moderately_aware</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Moderately Aware', 'label': 'Moderately Aware'}</t>
+          <t>Moderately Aware</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_aware',_'label':_'not_at_all_aware'}</t>
+          <t>not_at_all_aware</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Aware', 'label': 'Not at all Aware'}</t>
+          <t>Not at all Aware</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'highly_communicative',_'label':_'highly_communicative'}</t>
+          <t>highly_communicative</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Communicative', 'label': 'Highly Communicative'}</t>
+          <t>Highly Communicative</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'moderately_communicative',_'label':_'moderately_communicative'}</t>
+          <t>moderately_communicative</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Moderately Communicative', 'label': 'Moderately Communicative'}</t>
+          <t>Moderately Communicative</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_communicative',_'label':_'not_at_all_communicative'}</t>
+          <t>not_at_all_communicative</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all Communicative', 'label': 'Not at all Communicative'}</t>
+          <t>Not at all Communicative</t>
         </is>
       </c>
     </row>
